--- a/outputs/tppc_lims_master/TPPC_Instruments_final.xlsx
+++ b/outputs/tppc_lims_master/TPPC_Instruments_final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instruments" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="QA_Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1736,7 +1736,11 @@
           <t>آنالایزر گوگرد XRF</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>آنالایزر گوگرد XRF</t>
+        </is>
+      </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
           <t>EDXRF Sulfur Analyzer</t>
@@ -2491,7 +2495,11 @@
           <t>دستگاه رنگ سیبولت</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>رنگ‌سنج سیبولت</t>
+        </is>
+      </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Saybolt Colorimeter</t>

--- a/outputs/tppc_lims_master/TPPC_Instruments_final.xlsx
+++ b/outputs/tppc_lims_master/TPPC_Instruments_final.xlsx
@@ -2571,12 +2571,24 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>FT-IR Spectrometer</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
+          <t>InfraLUM FT-08 FT mid-IR Spectrometer</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Lumex</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>روسیه</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>INFRALUM FT-08</t>
+        </is>
+      </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr">
@@ -2596,7 +2608,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>Source: https://artinazma.net/product/infralum-ft-08-ftir-spectrometer/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2609,7 +2625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2642,12 +2658,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Model خالی</t>
+          <t>Serial Number خالی</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>مدل دستگاه را وارد کنید</t>
+          <t>شماره سریال را از پلاک/گواهی دستگاه وارد کنید</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2675,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>سازنده نامشخص</t>
+          <t>Calibration Date خالی</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>نام سازنده را تأیید/کامل کنید</t>
+          <t>تاریخ آخرین کالیبراسیون را وارد کنید</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2692,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>کشور نامشخص</t>
+          <t>Next Calibration Due خالی</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>کشور سازنده را وارد کنید</t>
+          <t>سررسید بعدی پس از تاریخ کالیبراسیون محاسبه می‌شود</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FTIR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Responsible Person خالی</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>مسئول دستگاه را مشخص کنید</t>
         </is>
       </c>
     </row>
